--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0107.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0107.xlsx
@@ -30547,7 +30547,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Có chuyện gì vậy?</t>
+          <t>Sao rồi?</t>
         </is>
       </c>
     </row>
@@ -30742,7 +30742,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Có chuyện gì vậy?</t>
+          <t>Sao thế?</t>
         </is>
       </c>
     </row>
@@ -31002,7 +31002,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Ta chưa xong đâu!</t>
+          <t>Tao chưa xong đâu!</t>
         </is>
       </c>
     </row>
@@ -31977,7 +31977,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Có chuyện gì vậy?</t>
+          <t>Sao rồi?</t>
         </is>
       </c>
     </row>
@@ -32042,7 +32042,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Có chuyện gì vậy?</t>
+          <t>Sao thế?</t>
         </is>
       </c>
     </row>
@@ -32497,7 +32497,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Cậu nghĩ cậu sẽ xuất hiện ở đâu?</t>
+          <t>Mày nghĩ mày sẽ xuất hiện ở đâu?</t>
         </is>
       </c>
     </row>
